--- a/contracts/review-export/naver/v1/naver-review-export-v1.xlsx
+++ b/contracts/review-export/naver/v1/naver-review-export-v1.xlsx
@@ -12,123 +12,213 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="69">
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>상품명</t>
+  </si>
+  <si>
+    <t>리뷰구분</t>
+  </si>
+  <si>
+    <t>구매자평점</t>
+  </si>
+  <si>
+    <t>포토/영상</t>
+  </si>
+  <si>
+    <t>리뷰상세내용</t>
+  </si>
+  <si>
+    <t>리뷰도움수</t>
+  </si>
+  <si>
+    <t>등록자</t>
+  </si>
+  <si>
+    <t>리뷰등록일</t>
+  </si>
+  <si>
+    <t>최종수정일</t>
+  </si>
   <si>
     <t>리뷰글번호</t>
   </si>
   <si>
-    <t>상품번호</t>
-  </si>
-  <si>
-    <t>상품명</t>
-  </si>
-  <si>
-    <t>구매자평점</t>
-  </si>
-  <si>
-    <t>리뷰상세내용</t>
-  </si>
-  <si>
-    <t>리뷰등록일</t>
+    <t>관련리뷰글번호</t>
+  </si>
+  <si>
+    <t>관련리뷰상세내용</t>
+  </si>
+  <si>
+    <t>전시상태</t>
+  </si>
+  <si>
+    <t>답글여부</t>
+  </si>
+  <si>
+    <t>답글등록일시</t>
+  </si>
+  <si>
+    <t>베스트리뷰</t>
+  </si>
+  <si>
+    <t>베스트리뷰선정일시</t>
+  </si>
+  <si>
+    <t>이벤트번호</t>
+  </si>
+  <si>
+    <t>혜택지급</t>
+  </si>
+  <si>
+    <t>혜택지급일시</t>
+  </si>
+  <si>
+    <t>유저정보 등록 항목</t>
   </si>
   <si>
     <t>상품주문번호</t>
   </si>
   <si>
-    <t>등록자</t>
+    <t>풀필먼트사</t>
+  </si>
+  <si>
+    <t>리뷰이동일</t>
+  </si>
+  <si>
+    <t>SKU-합성-11</t>
+  </si>
+  <si>
+    <t>합성 몰딩 세트 1호</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 배송이 늦었고 포장이 눌렸습니다.</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>REVIEWER-MUST-NOT-PERSIST</t>
+  </si>
+  <si>
+    <t>2026.05.05. 09:12:33</t>
   </si>
   <si>
     <t>1000000001</t>
   </si>
   <si>
-    <t>SKU-합성-11</t>
-  </si>
-  <si>
-    <t>합성 몰딩 세트 1호</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 배송이 늦었고 포장이 눌렸습니다.</t>
-  </si>
-  <si>
-    <t>2026.05.05.</t>
+    <t>노출</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>USERINFO-MUST-NOT-PERSIST</t>
   </si>
   <si>
     <t>ORDER-MUST-NOT-PERSIST</t>
   </si>
   <si>
-    <t>REVIEWER-MUST-NOT-PERSIST</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 색상이 사진과 달라 아쉽습니다.</t>
+  </si>
+  <si>
+    <t>2026.05.06. 14:03:07</t>
   </si>
   <si>
     <t>1000000002</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 색상이 사진과 달라 아쉽습니다.</t>
-  </si>
-  <si>
-    <t>2026.05.06.</t>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>2026.05.07. 10:22:41</t>
+  </si>
+  <si>
+    <t>SKU-합성-22</t>
+  </si>
+  <si>
+    <t>합성 마감재 2호</t>
+  </si>
+  <si>
+    <t>한달사용</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 무난하지만 접착력이 약합니다.</t>
+  </si>
+  <si>
+    <t>2026.05.07. 08:45:19</t>
   </si>
   <si>
     <t>1000000003</t>
   </si>
   <si>
-    <t>SKU-합성-22</t>
-  </si>
-  <si>
-    <t>합성 마감재 2호</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 무난하지만 접착력이 약합니다.</t>
-  </si>
-  <si>
-    <t>2026.05.07.</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 시공이 쉬웠습니다.</t>
+  </si>
+  <si>
+    <t>2026.05.08. 19:31:52</t>
+  </si>
+  <si>
+    <t>2026.05.09. 07:10:04</t>
   </si>
   <si>
     <t>1000000004</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 시공이 쉬웠습니다.</t>
-  </si>
-  <si>
-    <t>2026.05.08.</t>
+    <t>SKU-합성-33</t>
+  </si>
+  <si>
+    <t>합성 시공 키트 3호</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>https://example.invalid/synthetic-media-1</t>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 재구매 의사 있습니다.</t>
+  </si>
+  <si>
+    <t>2026.05.09. 11:58:26</t>
   </si>
   <si>
     <t>1000000005</t>
   </si>
   <si>
-    <t>SKU-합성-33</t>
-  </si>
-  <si>
-    <t>합성 시공 키트 3호</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 재구매 의사 있습니다.</t>
-  </si>
-  <si>
-    <t>2026.05.09.</t>
+    <t>2026.05.10. 09:05:13</t>
+  </si>
+  <si>
+    <t>2026.05.11. 00:00:00</t>
+  </si>
+  <si>
+    <t>합성 리뷰 본문 - 한 달 써보니 마감이 깔끔합니다.</t>
+  </si>
+  <si>
+    <t>2026.05.10. 16:40:58</t>
   </si>
   <si>
     <t>1000000006</t>
-  </si>
-  <si>
-    <t>합성 리뷰 본문 - 마감이 깔끔합니다.</t>
-  </si>
-  <si>
-    <t>2026.05.10.</t>
   </si>
 </sst>
 </file>
@@ -173,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -201,161 +291,518 @@
       <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T2" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="X2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y2" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="P3" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="S3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V3" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="X3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y3" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="S4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="W4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="X4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="S5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="W5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="X5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y5" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s" s="0">
+      <c r="I6" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="G6" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>15</v>
+      <c r="O6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="P6" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="R6" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="S6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="W6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="X6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y6" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="D7" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s" s="0">
+      <c r="I7" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Q7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="S7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="T7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="V7" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="F7" t="s" s="0">
+      <c r="W7" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="G7" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>15</v>
+      <c r="X7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Y7" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
